--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N50_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N50_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>18.94466455359024</v>
+        <v>3.078507989958414</v>
       </c>
       <c r="D2" t="n">
-        <v>20.52106256136718</v>
+        <v>3.334672666222168</v>
       </c>
       <c r="E2" t="n">
-        <v>11.71315041016987</v>
+        <v>1.903386941652604</v>
       </c>
       <c r="F2" t="n">
-        <v>9.314903327307187</v>
+        <v>1.513671790687418</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.97114187715826</v>
+        <v>4.057810555038217</v>
       </c>
       <c r="D3" t="n">
-        <v>23.69435049900358</v>
+        <v>3.850331956088082</v>
       </c>
       <c r="E3" t="n">
-        <v>11.71315041016987</v>
+        <v>1.903386941652604</v>
       </c>
       <c r="F3" t="n">
-        <v>9.314903327307187</v>
+        <v>1.513671790687418</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.08996446430649</v>
+        <v>2.289619225449804</v>
       </c>
       <c r="D4" t="n">
-        <v>15.24169365692947</v>
+        <v>2.476775219251039</v>
       </c>
       <c r="E4" t="n">
-        <v>11.71315041016987</v>
+        <v>1.903386941652604</v>
       </c>
       <c r="F4" t="n">
-        <v>9.314903327307187</v>
+        <v>1.513671790687418</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>18.34494970453437</v>
+        <v>2.981054326986836</v>
       </c>
       <c r="D5" t="n">
-        <v>17.05343873722909</v>
+        <v>2.771183794799728</v>
       </c>
       <c r="E5" t="n">
-        <v>11.71315041016987</v>
+        <v>1.903386941652604</v>
       </c>
       <c r="F5" t="n">
-        <v>9.314903327307187</v>
+        <v>1.513671790687418</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.95274082592793</v>
+        <v>5.679820384213289</v>
       </c>
       <c r="D6" t="n">
-        <v>4.955574424389805</v>
+        <v>0.8052808439633434</v>
       </c>
       <c r="E6" t="n">
-        <v>11.71315041016987</v>
+        <v>1.903386941652604</v>
       </c>
       <c r="F6" t="n">
-        <v>9.314903327307187</v>
+        <v>1.513671790687418</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>26.33784116116592</v>
+        <v>4.279899188689462</v>
       </c>
       <c r="D7" t="n">
-        <v>25.07955792137661</v>
+        <v>4.075428162223699</v>
       </c>
       <c r="E7" t="n">
-        <v>11.71315041016987</v>
+        <v>1.903386941652604</v>
       </c>
       <c r="F7" t="n">
-        <v>9.314903327307187</v>
+        <v>1.513671790687418</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>43.34465903151462</v>
+        <v>7.043507092621126</v>
       </c>
       <c r="D8" t="n">
-        <v>9.958402324309613</v>
+        <v>1.618240377700312</v>
       </c>
       <c r="E8" t="n">
-        <v>11.71315041016987</v>
+        <v>1.903386941652604</v>
       </c>
       <c r="F8" t="n">
-        <v>9.314903327307187</v>
+        <v>1.513671790687418</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>23.06375622452441</v>
+        <v>3.747860386485217</v>
       </c>
       <c r="D9" t="n">
-        <v>21.99365098988837</v>
+        <v>3.573968285856859</v>
       </c>
       <c r="E9" t="n">
-        <v>11.71315041016987</v>
+        <v>1.903386941652604</v>
       </c>
       <c r="F9" t="n">
-        <v>9.314903327307187</v>
+        <v>1.513671790687418</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>2.499254750410925</v>
+        <v>0.4061288969417753</v>
       </c>
       <c r="D10" t="n">
-        <v>3.52759809513496</v>
+        <v>0.5732346904594311</v>
       </c>
       <c r="E10" t="n">
-        <v>11.71315041016987</v>
+        <v>1.903386941652604</v>
       </c>
       <c r="F10" t="n">
-        <v>9.314903327307187</v>
+        <v>1.513671790687418</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>32.14685165614903</v>
+        <v>5.223863394124218</v>
       </c>
       <c r="D11" t="n">
-        <v>5.196333583984902</v>
+        <v>0.8444042073975466</v>
       </c>
       <c r="E11" t="n">
-        <v>11.71315041016987</v>
+        <v>1.903386941652604</v>
       </c>
       <c r="F11" t="n">
-        <v>9.314903327307187</v>
+        <v>1.513671790687418</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>20.90553734106459</v>
+        <v>3.397149817922996</v>
       </c>
       <c r="D12" t="n">
-        <v>19.27005219204727</v>
+        <v>3.131383481207681</v>
       </c>
       <c r="E12" t="n">
-        <v>11.71315041016987</v>
+        <v>1.903386941652604</v>
       </c>
       <c r="F12" t="n">
-        <v>9.314903327307187</v>
+        <v>1.513671790687418</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>38.25389229650195</v>
+        <v>6.216257498181568</v>
       </c>
       <c r="D13" t="n">
-        <v>5.266737783375992</v>
+        <v>0.8558448897985986</v>
       </c>
       <c r="E13" t="n">
-        <v>11.71315041016987</v>
+        <v>1.903386941652604</v>
       </c>
       <c r="F13" t="n">
-        <v>9.314903327307187</v>
+        <v>1.513671790687418</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>22.69581279984339</v>
+        <v>3.688069579974551</v>
       </c>
       <c r="D14" t="n">
-        <v>16.47566480795836</v>
+        <v>2.677295531293233</v>
       </c>
       <c r="E14" t="n">
-        <v>11.71315041016987</v>
+        <v>1.903386941652604</v>
       </c>
       <c r="F14" t="n">
-        <v>9.314903327307187</v>
+        <v>1.513671790687418</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>33.04318939053837</v>
+        <v>5.369518275962486</v>
       </c>
       <c r="D15" t="n">
-        <v>8.847750359441649</v>
+        <v>1.437759433409268</v>
       </c>
       <c r="E15" t="n">
-        <v>11.71315041016987</v>
+        <v>1.903386941652604</v>
       </c>
       <c r="F15" t="n">
-        <v>9.314903327307187</v>
+        <v>1.513671790687418</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>32.29132286038288</v>
+        <v>5.247339964812219</v>
       </c>
       <c r="D16" t="n">
-        <v>11.84618498781071</v>
+        <v>1.925005060519241</v>
       </c>
       <c r="E16" t="n">
-        <v>11.71315041016987</v>
+        <v>1.903386941652604</v>
       </c>
       <c r="F16" t="n">
-        <v>9.314903327307187</v>
+        <v>1.513671790687418</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>34.58598653562018</v>
+        <v>5.620222812038279</v>
       </c>
       <c r="D17" t="n">
-        <v>7.984297761517915</v>
+        <v>1.297448386246661</v>
       </c>
       <c r="E17" t="n">
-        <v>11.71315041016987</v>
+        <v>1.903386941652604</v>
       </c>
       <c r="F17" t="n">
-        <v>9.314903327307187</v>
+        <v>1.513671790687418</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>21.06318221983584</v>
+        <v>3.422767110723324</v>
       </c>
       <c r="D18" t="n">
-        <v>9.492036948521566</v>
+        <v>1.542456004134755</v>
       </c>
       <c r="E18" t="n">
-        <v>11.71315041016987</v>
+        <v>1.903386941652604</v>
       </c>
       <c r="F18" t="n">
-        <v>9.314903327307187</v>
+        <v>1.513671790687418</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>10.74660732572439</v>
+        <v>1.746323690430214</v>
       </c>
       <c r="D19" t="n">
-        <v>20.37832817539279</v>
+        <v>3.311478328501328</v>
       </c>
       <c r="E19" t="n">
-        <v>11.71315041016987</v>
+        <v>1.903386941652604</v>
       </c>
       <c r="F19" t="n">
-        <v>9.314903327307187</v>
+        <v>1.513671790687418</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>16.19298971510092</v>
+        <v>2.631360828703901</v>
       </c>
       <c r="D20" t="n">
-        <v>12.0280684905921</v>
+        <v>1.954561129721217</v>
       </c>
       <c r="E20" t="n">
-        <v>11.71315041016987</v>
+        <v>1.903386941652604</v>
       </c>
       <c r="F20" t="n">
-        <v>9.314903327307187</v>
+        <v>1.513671790687418</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>46.26790844225786</v>
+        <v>7.518535121866901</v>
       </c>
       <c r="D21" t="n">
-        <v>31.18626535359578</v>
+        <v>5.067768119959315</v>
       </c>
       <c r="E21" t="n">
-        <v>11.71315041016987</v>
+        <v>1.903386941652604</v>
       </c>
       <c r="F21" t="n">
-        <v>9.314903327307187</v>
+        <v>1.513671790687418</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>39.96745483852326</v>
+        <v>6.49471141126003</v>
       </c>
       <c r="D22" t="n">
-        <v>13.87243469778988</v>
+        <v>2.254270638390855</v>
       </c>
       <c r="E22" t="n">
-        <v>11.71315041016987</v>
+        <v>1.903386941652604</v>
       </c>
       <c r="F22" t="n">
-        <v>9.314903327307187</v>
+        <v>1.513671790687418</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>38.33757163660022</v>
+        <v>6.229855390947536</v>
       </c>
       <c r="D23" t="n">
-        <v>4.41870222048161</v>
+        <v>0.7180391108282616</v>
       </c>
       <c r="E23" t="n">
-        <v>11.71315041016987</v>
+        <v>1.903386941652604</v>
       </c>
       <c r="F23" t="n">
-        <v>9.314903327307187</v>
+        <v>1.513671790687418</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>40.34568990923675</v>
+        <v>6.556174610250972</v>
       </c>
       <c r="D24" t="n">
-        <v>35.66315539275609</v>
+        <v>5.795262751322865</v>
       </c>
       <c r="E24" t="n">
-        <v>11.71315041016987</v>
+        <v>1.903386941652604</v>
       </c>
       <c r="F24" t="n">
-        <v>9.314903327307187</v>
+        <v>1.513671790687418</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>35.57367087506081</v>
+        <v>5.780721517197382</v>
       </c>
       <c r="D25" t="n">
-        <v>34.29114027442113</v>
+        <v>5.572310294593434</v>
       </c>
       <c r="E25" t="n">
-        <v>11.71315041016987</v>
+        <v>1.903386941652604</v>
       </c>
       <c r="F25" t="n">
-        <v>9.314903327307187</v>
+        <v>1.513671790687418</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>36.59527997732781</v>
+        <v>5.946732996315768</v>
       </c>
       <c r="D26" t="n">
-        <v>7.946810214153662</v>
+        <v>1.29135665979997</v>
       </c>
       <c r="E26" t="n">
-        <v>11.71315041016987</v>
+        <v>1.903386941652604</v>
       </c>
       <c r="F26" t="n">
-        <v>9.314903327307187</v>
+        <v>1.513671790687418</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>3.4810725645386</v>
+        <v>0.5656742917375226</v>
       </c>
       <c r="D27" t="n">
-        <v>3.307414145586571</v>
+        <v>0.5374547986578179</v>
       </c>
       <c r="E27" t="n">
-        <v>11.71315041016987</v>
+        <v>1.903386941652604</v>
       </c>
       <c r="F27" t="n">
-        <v>9.314903327307187</v>
+        <v>1.513671790687418</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
